--- a/Scenario_data_EUR_plus.xlsx
+++ b/Scenario_data_EUR_plus.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6198770ba2d695f8/Documents/MasterThesis/CIRED/EOLES/Passa_Philippe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="768" documentId="8_{BA1AFA72-7ABC-48D4-802B-4BE08DE679D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D79A68A-5F43-4742-B446-69CD8389626B}"/>
+  <xr:revisionPtr revIDLastSave="962" documentId="8_{BA1AFA72-7ABC-48D4-802B-4BE08DE679D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3581754C-F941-4C51-853D-A850322D9914}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="9" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -183,7 +183,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2019" uniqueCount="638">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2021" uniqueCount="640">
   <si>
     <t>tech</t>
   </si>
@@ -2097,6 +2097,12 @@
   </si>
   <si>
     <t>Total clim elec 2019 corrigé climat 2050</t>
+  </si>
+  <si>
+    <t>min_CF_hourly_nuclear</t>
+  </si>
+  <si>
+    <t>max_CF_hourly_nuclear</t>
   </si>
 </sst>
 </file>
@@ -3513,7 +3519,7 @@
       </c>
       <c r="B14" cm="1">
         <f t="array" ref="B14">INDEX(Data_EOLES!$J$1:$EK$191,MATCH("annual_production"&amp;"_"&amp;$A14,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))/INDEX(tech_parameters!$A$1:$CA$301, MATCH($A14,tech_parameters!$A$1:$A$301,0), MATCH("capacity_factor",tech_parameters!$A$1:$CA$1,0))/8.76</f>
-        <v>12.727467384213961</v>
+        <v>2.0957142857142861</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -4084,7 +4090,7 @@
       </c>
       <c r="B2" s="37">
         <f>max_cap!B2</f>
-        <v>25.671469999999999</v>
+        <v>29.298100000000002</v>
       </c>
       <c r="C2">
         <f>max_cap!C2</f>
@@ -4129,7 +4135,7 @@
       </c>
       <c r="B3" s="37">
         <f>max_cap!B3</f>
-        <v>18.10886</v>
+        <v>18.49108</v>
       </c>
       <c r="C3">
         <f>max_cap!C3</f>
@@ -4174,7 +4180,7 @@
       </c>
       <c r="B4" s="37">
         <f>max_cap!B4</f>
-        <v>72.968890000000002</v>
+        <v>80.655379999999994</v>
       </c>
       <c r="C4">
         <f>max_cap!C4</f>
@@ -4219,7 +4225,7 @@
       </c>
       <c r="B5" s="37">
         <f>max_cap!B5</f>
-        <v>60.912689999999998</v>
+        <v>69.274829999999994</v>
       </c>
       <c r="C5">
         <f>max_cap!C5</f>
@@ -4227,7 +4233,7 @@
       </c>
       <c r="D5" s="27">
         <f>max_cap!D5</f>
-        <v>59.4</v>
+        <v>62.370000000000005</v>
       </c>
       <c r="E5">
         <f>max_cap!E5</f>
@@ -4264,7 +4270,7 @@
       </c>
       <c r="B6" s="37">
         <f>max_cap!B6</f>
-        <v>69.920720000000003</v>
+        <v>85.939499999999995</v>
       </c>
       <c r="C6">
         <f>max_cap!C6</f>
@@ -4272,7 +4278,7 @@
       </c>
       <c r="D6" s="27">
         <f>max_cap!D6</f>
-        <v>84.6</v>
+        <v>88.83</v>
       </c>
       <c r="E6">
         <f>max_cap!E6</f>
@@ -4309,7 +4315,7 @@
       </c>
       <c r="B7" s="37">
         <f>max_cap!B7</f>
-        <v>32.991320000000002</v>
+        <v>41.819139999999997</v>
       </c>
       <c r="C7">
         <f>max_cap!C7</f>
@@ -4317,7 +4323,7 @@
       </c>
       <c r="D7" s="27">
         <f>max_cap!D7</f>
-        <v>36</v>
+        <v>37.800000000000004</v>
       </c>
       <c r="E7">
         <f>max_cap!E7</f>
@@ -4370,7 +4376,7 @@
       </c>
       <c r="F8">
         <f>max_cap!F8</f>
-        <v>3.9</v>
+        <v>4.29</v>
       </c>
       <c r="G8">
         <f>max_cap!G8</f>
@@ -4399,7 +4405,7 @@
       </c>
       <c r="B9" s="37">
         <f>max_cap!B9</f>
-        <v>1.25</v>
+        <v>1.39303</v>
       </c>
       <c r="C9">
         <f>max_cap!C9</f>
@@ -4577,46 +4583,7 @@
       <c r="A13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="37">
-        <f>max_cap!B13</f>
-        <v>1.9711362838075168</v>
-      </c>
-      <c r="C13">
-        <f>max_cap!C13</f>
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <f>max_cap!D13</f>
-        <v>8.2543027748507196</v>
-      </c>
-      <c r="E13">
-        <f>max_cap!E13</f>
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <f>max_cap!F13</f>
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <f>max_cap!G13</f>
-        <v>4.82</v>
-      </c>
-      <c r="H13">
-        <f>max_cap!H13</f>
-        <v>5</v>
-      </c>
-      <c r="I13">
-        <f>max_cap!I13</f>
-        <v>2.1074815595363541</v>
-      </c>
-      <c r="J13">
-        <f>max_cap!J13</f>
-        <v>0.3</v>
-      </c>
-      <c r="K13">
-        <f>max_cap!K13</f>
-        <v>0</v>
-      </c>
+      <c r="B13" s="37"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
@@ -4624,7 +4591,7 @@
       </c>
       <c r="B14" s="37">
         <f>max_cap!B14</f>
-        <v>12.727467384213961</v>
+        <v>2.0957142857142861</v>
       </c>
       <c r="C14">
         <f>max_cap!C14</f>
@@ -4667,46 +4634,16 @@
       <c r="A15" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="109">
-        <f>max_cap!B15</f>
-        <v>0</v>
-      </c>
-      <c r="C15" s="109">
-        <f>max_cap!C15</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="109">
-        <f>max_cap!D15</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="109">
-        <f>max_cap!E15</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="109">
-        <f>max_cap!F15</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="109">
-        <f>max_cap!G15</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="109">
-        <f>max_cap!H15</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="109">
-        <f>max_cap!I15</f>
-        <v>0</v>
-      </c>
-      <c r="J15" s="109">
-        <f>max_cap!J15</f>
-        <v>0</v>
-      </c>
-      <c r="K15" s="109">
-        <f>max_cap!K15</f>
-        <v>0</v>
-      </c>
+      <c r="B15" s="109"/>
+      <c r="C15" s="109"/>
+      <c r="D15" s="109"/>
+      <c r="E15" s="109"/>
+      <c r="F15" s="109"/>
+      <c r="G15" s="109"/>
+      <c r="H15" s="109"/>
+      <c r="I15" s="109"/>
+      <c r="J15" s="109"/>
+      <c r="K15" s="109"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
@@ -4803,8 +4740,7 @@
         <v>9</v>
       </c>
       <c r="B20">
-        <f>max_cap!B20</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C20">
         <f>max_cap!C20</f>
@@ -4967,6 +4903,10 @@
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>16</v>
+      </c>
+      <c r="B33">
+        <f>max_cap!B33</f>
+        <v>88.417000000000002</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
@@ -5250,7 +5190,7 @@
       </c>
       <c r="B20">
         <f>20*min_cap!B20</f>
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="C20">
         <f>20*exist_cap!C20</f>
@@ -5898,7 +5838,7 @@
       </c>
       <c r="B2" s="28" cm="1">
         <f t="array" ref="B2">INDEX(Data_EOLES!$J$1:$EK$191,MATCH("biomass_potential_"&amp;$A2,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>160.75888</v>
+        <v>162.51201</v>
       </c>
       <c r="C2">
         <v>56</v>
@@ -5934,7 +5874,7 @@
       </c>
       <c r="B3" s="28" cm="1">
         <f t="array" ref="B3">INDEX(Data_EOLES!$J$1:$EK$191,MATCH("biomass_potential_"&amp;$A3,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>7.9070499999999999</v>
+        <v>8.1163500000000006</v>
       </c>
       <c r="C3">
         <v>16</v>
@@ -6091,7 +6031,7 @@
       </c>
       <c r="B2" s="37" cm="1">
         <f t="array" ref="B2">INDEX(Data_EOLES!$J$1:$EK$191,MATCH("max_cap"&amp;"_"&amp;$A2,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>25.671469999999999</v>
+        <v>29.298100000000002</v>
       </c>
       <c r="C2">
         <f>6.7</f>
@@ -6136,7 +6076,7 @@
       </c>
       <c r="B3" s="37" cm="1">
         <f t="array" ref="B3">INDEX(Data_EOLES!$J$1:$EK$191,MATCH("max_cap"&amp;"_"&amp;$A3,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>18.10886</v>
+        <v>18.49108</v>
       </c>
       <c r="C3">
         <f>4.1</f>
@@ -6181,7 +6121,7 @@
       </c>
       <c r="B4" s="37" cm="1">
         <f t="array" ref="B4">INDEX(Data_EOLES!$J$1:$EK$191,MATCH("max_cap"&amp;"_"&amp;$A4,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>72.968890000000002</v>
+        <v>80.655379999999994</v>
       </c>
       <c r="C4">
         <f>89.4</f>
@@ -6226,15 +6166,15 @@
       </c>
       <c r="B5" s="37" cm="1">
         <f t="array" ref="B5">INDEX(Data_EOLES!$J$1:$EK$191,MATCH("max_cap"&amp;"_"&amp;$A5,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>60.912689999999998</v>
+        <v>69.274829999999994</v>
       </c>
       <c r="C5">
         <f>50.1</f>
         <v>50.1</v>
       </c>
       <c r="D5" s="27">
-        <f>59.4</f>
-        <v>59.4</v>
+        <f>1.05*59.4</f>
+        <v>62.370000000000005</v>
       </c>
       <c r="E5">
         <f>13.6</f>
@@ -6271,15 +6211,15 @@
       </c>
       <c r="B6" s="37" cm="1">
         <f t="array" ref="B6">INDEX(Data_EOLES!$J$1:$EK$191,MATCH("max_cap"&amp;"_"&amp;$A6,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>69.920720000000003</v>
+        <v>85.939499999999995</v>
       </c>
       <c r="C6">
         <f>70.9</f>
         <v>70.900000000000006</v>
       </c>
       <c r="D6" s="27">
-        <f>84.6</f>
-        <v>84.6</v>
+        <f>1.05*84.6</f>
+        <v>88.83</v>
       </c>
       <c r="E6">
         <f>19.4</f>
@@ -6316,15 +6256,15 @@
       </c>
       <c r="B7" s="37" cm="1">
         <f t="array" ref="B7">INDEX(Data_EOLES!$J$1:$EK$191,MATCH("max_cap"&amp;"_"&amp;$A7,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>32.991320000000002</v>
+        <v>41.819139999999997</v>
       </c>
       <c r="C7">
         <f>30.6</f>
         <v>30.6</v>
       </c>
       <c r="D7" s="27">
-        <f>36</f>
-        <v>36</v>
+        <f>1.05*36</f>
+        <v>37.800000000000004</v>
       </c>
       <c r="E7">
         <f>8.2</f>
@@ -6376,8 +6316,8 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="F8">
-        <f>3.9</f>
-        <v>3.9</v>
+        <f>1.1*3.9</f>
+        <v>4.29</v>
       </c>
       <c r="G8">
         <f>0.1</f>
@@ -6406,7 +6346,7 @@
       </c>
       <c r="B9" s="37" cm="1">
         <f t="array" ref="B9">INDEX(Data_EOLES!$J$1:$EK$191,MATCH("max_cap"&amp;"_"&amp;$A9,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>1.25</v>
+        <v>1.39303</v>
       </c>
       <c r="C9">
         <f>3.7</f>
@@ -6631,7 +6571,7 @@
       </c>
       <c r="B14" s="31" cm="1">
         <f t="array" ref="B14">INDEX(Data_EOLES!$J$1:$EK$191,MATCH("annual_production"&amp;"_"&amp;$A14,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))/INDEX(tech_parameters!$A$1:$CA$301, MATCH($A14,tech_parameters!$A$1:$A$301,0), MATCH("capacity_factor",tech_parameters!$A$1:$CA$1,0))/8.76</f>
-        <v>12.727467384213961</v>
+        <v>2.0957142857142861</v>
       </c>
       <c r="C14">
         <f>0</f>
@@ -6719,7 +6659,6 @@
       <c r="A16" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="109"/>
       <c r="C16" s="109"/>
       <c r="D16" s="109"/>
       <c r="E16" s="109"/>
@@ -6734,7 +6673,6 @@
       <c r="A17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="109"/>
       <c r="C17" s="109"/>
       <c r="D17" s="109"/>
       <c r="E17" s="109"/>
@@ -6749,7 +6687,6 @@
       <c r="A18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="109"/>
       <c r="C18" s="109"/>
       <c r="D18" s="109"/>
       <c r="E18" s="109"/>
@@ -6844,7 +6781,6 @@
       <c r="A21" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B21" s="109"/>
       <c r="C21" s="109"/>
       <c r="D21" s="109"/>
       <c r="E21" s="109"/>
@@ -6859,7 +6795,6 @@
       <c r="A22" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="109"/>
       <c r="C22" s="109"/>
       <c r="D22" s="109"/>
       <c r="E22" s="109"/>
@@ -6874,7 +6809,6 @@
       <c r="A23" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="109"/>
       <c r="C23" s="109"/>
       <c r="D23" s="109"/>
       <c r="E23" s="109"/>
@@ -6889,7 +6823,6 @@
       <c r="A24" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="109"/>
       <c r="C24" s="109"/>
       <c r="D24" s="109"/>
       <c r="E24" s="109"/>
@@ -6904,7 +6837,6 @@
       <c r="A25" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="109"/>
       <c r="C25" s="109"/>
       <c r="D25" s="109"/>
       <c r="E25" s="109"/>
@@ -6919,7 +6851,6 @@
       <c r="A26" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B26" s="109"/>
       <c r="C26" s="109"/>
       <c r="D26" s="109"/>
       <c r="E26" s="109"/>
@@ -6963,9 +6894,6 @@
       <c r="A32" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B32">
-        <v>7</v>
-      </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
@@ -7048,6 +6976,36 @@
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>540</v>
+      </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -35484,7 +35442,7 @@
       </c>
       <c r="C9" s="33" cm="1">
         <f t="array" ref="C9">INDEX(Data_EOLES!$J$1:$EK$191,MATCH(A9,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>29.77571</v>
+        <v>27.616320000000002</v>
       </c>
       <c r="D9" t="s">
         <v>455</v>
@@ -35499,7 +35457,7 @@
       </c>
       <c r="C10" s="33" cm="1">
         <f t="array" ref="C10">INDEX(Data_EOLES!$J$1:$EK$191,MATCH(A10,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>11.59836</v>
+        <v>7.6760799999999998</v>
       </c>
       <c r="D10" t="s">
         <v>455</v>
@@ -35514,7 +35472,7 @@
       </c>
       <c r="C11" s="33" cm="1">
         <f t="array" ref="C11">INDEX(Data_EOLES!$J$1:$EK$191,MATCH(A11,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>9.3402799999999999</v>
+        <v>3.3402799999999999</v>
       </c>
       <c r="D11" s="38" t="s">
         <v>442</v>
@@ -35529,7 +35487,7 @@
       </c>
       <c r="C12" s="33" cm="1">
         <f t="array" ref="C12">INDEX(Data_EOLES!$J$1:$EK$191,MATCH(A12,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>15.451510000000001</v>
+        <v>16.651789999999998</v>
       </c>
       <c r="D12" s="38" t="s">
         <v>442</v>
@@ -35547,7 +35505,7 @@
       </c>
       <c r="C14" s="33" cm="1">
         <f t="array" ref="C14">INDEX(Data_EOLES!$J$1:$EK$191,MATCH(A14,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>102.85942</v>
+        <v>96.298770000000005</v>
       </c>
       <c r="D14" t="s">
         <v>455</v>
@@ -35562,7 +35520,7 @@
       </c>
       <c r="C15" s="33" cm="1">
         <f t="array" ref="C15">INDEX(Data_EOLES!$J$1:$EK$191,MATCH(A15,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>107.40139000000001</v>
+        <v>103.73578000000001</v>
       </c>
       <c r="D15" t="s">
         <v>455</v>
@@ -35577,7 +35535,7 @@
       </c>
       <c r="C16" s="33" cm="1">
         <f t="array" ref="C16">INDEX(Data_EOLES!$J$1:$EK$191,MATCH(A16,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>66.479370000000003</v>
+        <v>66.323310000000006</v>
       </c>
       <c r="D16" t="s">
         <v>455</v>
@@ -35592,7 +35550,7 @@
       </c>
       <c r="C17" s="33" cm="1">
         <f t="array" ref="C17">INDEX(Data_EOLES!$J$1:$EK$191,MATCH(A17,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>47.690150000000003</v>
+        <v>47.44162</v>
       </c>
       <c r="D17" t="s">
         <v>455</v>
@@ -35607,7 +35565,7 @@
       </c>
       <c r="C18" s="33" cm="1">
         <f t="array" ref="C18">INDEX(Data_EOLES!$J$1:$EK$191,MATCH(A18,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>116.83425</v>
+        <v>113.93828000000001</v>
       </c>
       <c r="D18" t="s">
         <v>455</v>
@@ -35622,7 +35580,7 @@
       </c>
       <c r="C19" s="33" cm="1">
         <f t="array" ref="C19">INDEX(Data_EOLES!$J$1:$EK$191,MATCH(A19,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>11.971550000000001</v>
+        <v>12.214309999999999</v>
       </c>
       <c r="D19" t="s">
         <v>455</v>
@@ -35637,7 +35595,7 @@
       </c>
       <c r="C20" s="33" cm="1">
         <f t="array" ref="C20">INDEX(Data_EOLES!$J$1:$EK$191,MATCH(A20,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>22.057500000000001</v>
+        <v>20.9709</v>
       </c>
       <c r="D20" t="s">
         <v>455</v>
@@ -35667,7 +35625,7 @@
       </c>
       <c r="C22" s="33" cm="1">
         <f t="array" ref="C22">INDEX(Data_EOLES!$J$1:$EK$191,MATCH(A22,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>41.2226</v>
+        <v>39.980899999999998</v>
       </c>
       <c r="D22" t="s">
         <v>455</v>
@@ -35685,7 +35643,7 @@
       </c>
       <c r="C24" s="35">
         <f>SUM(C14:C22)</f>
-        <v>519.77072999999996</v>
+        <v>504.1583700000001</v>
       </c>
       <c r="D24" s="36" t="s">
         <v>423</v>
@@ -35695,11 +35653,11 @@
       <c r="A25" s="32"/>
       <c r="B25" s="116" t="str">
         <f>"Total chauffage elec " &amp;year_simulated</f>
-        <v>Total chauffage elec 2050</v>
+        <v>Total chauffage elec 2060</v>
       </c>
       <c r="C25" s="117">
         <f>SUM(C9:C10)</f>
-        <v>41.374070000000003</v>
+        <v>35.292400000000001</v>
       </c>
       <c r="D25" s="118" t="s">
         <v>455</v>
@@ -35736,7 +35694,7 @@
       </c>
       <c r="C28" s="117">
         <f>SUM(C11:C12)</f>
-        <v>24.791789999999999</v>
+        <v>19.992069999999998</v>
       </c>
       <c r="D28" s="118"/>
     </row>
@@ -35768,11 +35726,11 @@
       </c>
       <c r="B31" t="str">
         <f>"coef elec 2019 "&amp;year_simulated</f>
-        <v>coef elec 2019 2050</v>
+        <v>coef elec 2019 2060</v>
       </c>
       <c r="C31" s="120">
         <f>C25/C26</f>
-        <v>0.61603241922966412</v>
+        <v>0.5254803927295767</v>
       </c>
       <c r="D31" s="36" t="s">
         <v>423</v>
@@ -35787,7 +35745,7 @@
       </c>
       <c r="C32" s="120">
         <f>C28/C29</f>
-        <v>0.95919465037848095</v>
+        <v>0.77349342641221619</v>
       </c>
       <c r="D32" s="36" t="s">
         <v>423</v>
@@ -35814,7 +35772,7 @@
       </c>
       <c r="C36" s="33" cm="1">
         <f t="array" ref="C36">INDEX(Data_EOLES!$J$1:$EK$191,MATCH(A36,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>17.393750000000001</v>
+        <v>14.93263</v>
       </c>
       <c r="D36" t="s">
         <v>455</v>
@@ -35829,7 +35787,7 @@
       </c>
       <c r="C37" s="33" cm="1">
         <f t="array" ref="C37">INDEX(Data_EOLES!$J$1:$EK$191,MATCH(A37,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>12.41038</v>
+        <v>6.4014800000000003</v>
       </c>
       <c r="D37" t="s">
         <v>455</v>
@@ -35853,7 +35811,7 @@
       </c>
       <c r="C41" s="33" cm="1">
         <f t="array" ref="C41">INDEX(Data_EOLES!$J$1:$EK$191,MATCH(A41,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>19.988399999999999</v>
+        <v>17.132999999999999</v>
       </c>
       <c r="D41" t="s">
         <v>455</v>
@@ -35868,7 +35826,7 @@
       </c>
       <c r="C42" s="33" cm="1">
         <f t="array" ref="C42">INDEX(Data_EOLES!$J$1:$EK$191,MATCH(A42,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>16.657039999999999</v>
+        <v>10.39766</v>
       </c>
       <c r="D42" t="s">
         <v>455</v>
@@ -35883,7 +35841,7 @@
       </c>
       <c r="C43" s="33" cm="1">
         <f t="array" ref="C43">INDEX(Data_EOLES!$J$1:$EK$191,MATCH(A43,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>6.6315299999999997</v>
+        <v>6.0952999999999999</v>
       </c>
       <c r="D43" t="s">
         <v>455</v>
@@ -35898,7 +35856,7 @@
       </c>
       <c r="C44" s="33" cm="1">
         <f t="array" ref="C44">INDEX(Data_EOLES!$J$1:$EK$191,MATCH(A44,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>30.53875</v>
+        <v>22.76362</v>
       </c>
       <c r="D44" t="s">
         <v>455</v>
@@ -35913,7 +35871,7 @@
       </c>
       <c r="C45" s="33" cm="1">
         <f t="array" ref="C45">INDEX(Data_EOLES!$J$1:$EK$191,MATCH(A45,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>42.323689999999999</v>
+        <v>42.382829999999998</v>
       </c>
       <c r="D45" t="s">
         <v>455</v>
@@ -35928,7 +35886,7 @@
       </c>
       <c r="C46" s="33" cm="1">
         <f t="array" ref="C46">INDEX(Data_EOLES!$J$1:$EK$191,MATCH(A46,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>10.12904</v>
+        <v>10.57793</v>
       </c>
       <c r="D46" t="s">
         <v>455</v>
@@ -35943,7 +35901,7 @@
       </c>
       <c r="C47" s="33" cm="1">
         <f t="array" ref="C47">INDEX(Data_EOLES!$J$1:$EK$191,MATCH(A47,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>3.0137999999999998</v>
+        <v>2.9594999999999998</v>
       </c>
       <c r="D47" t="s">
         <v>455</v>
@@ -35987,7 +35945,7 @@
       </c>
       <c r="C50" s="33" cm="1">
         <f t="array" ref="C50">INDEX(Data_EOLES!$J$1:$EK$191,MATCH(A50,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>6.36191</v>
+        <v>7.8542899999999998</v>
       </c>
       <c r="D50" t="s">
         <v>455</v>
@@ -36002,7 +35960,7 @@
       </c>
       <c r="C51" s="33" cm="1">
         <f t="array" ref="C51">INDEX(Data_EOLES!$J$1:$EK$191,MATCH(A51,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>2.59578</v>
+        <v>3.0157500000000002</v>
       </c>
       <c r="D51" t="s">
         <v>455</v>
@@ -36032,7 +35990,7 @@
       </c>
       <c r="C53" s="33" cm="1">
         <f t="array" ref="C53">INDEX(Data_EOLES!$J$1:$EK$191,MATCH(A53,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>1.3794</v>
+        <v>1.2272000000000001</v>
       </c>
       <c r="D53" t="s">
         <v>455</v>
@@ -36050,7 +36008,7 @@
       </c>
       <c r="C55" s="35">
         <f xml:space="preserve"> SUM(C41:C47)+SUM(C49:C51)+C53 - C48</f>
-        <v>142.65514000000002</v>
+        <v>127.44288</v>
       </c>
       <c r="D55" s="36" t="s">
         <v>423</v>
@@ -36060,11 +36018,11 @@
       <c r="A56" s="32"/>
       <c r="B56" t="str">
         <f>"Total chauffage gaz "&amp;year_simulated</f>
-        <v>Total chauffage gaz 2050</v>
+        <v>Total chauffage gaz 2060</v>
       </c>
       <c r="C56" s="33">
         <f>SUM(C36:C37)</f>
-        <v>29.804130000000001</v>
+        <v>21.334109999999999</v>
       </c>
       <c r="D56" t="s">
         <v>455</v>
@@ -36089,11 +36047,11 @@
       </c>
       <c r="B58" t="str">
         <f>"coef gaz 2019 "&amp;year_simulated</f>
-        <v>coef gaz 2019 2050</v>
+        <v>coef gaz 2019 2060</v>
       </c>
       <c r="C58" s="35">
         <f>C56/C57</f>
-        <v>0.17327994647438125</v>
+        <v>0.12403560979228588</v>
       </c>
       <c r="D58" s="36" t="s">
         <v>423</v>
@@ -36126,7 +36084,7 @@
       </c>
       <c r="C64" s="33" cm="1">
         <f t="array" ref="C64">INDEX(Data_EOLES!$J$1:$EK$191,MATCH(A64,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>3.1684999999999999</v>
+        <v>3.0392999999999999</v>
       </c>
       <c r="D64" t="s">
         <v>455</v>
@@ -36141,7 +36099,7 @@
       </c>
       <c r="C65" s="33" cm="1">
         <f t="array" ref="C65">INDEX(Data_EOLES!$J$1:$EK$191,MATCH(A65,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>0.90980000000000005</v>
+        <v>0.90059999999999996</v>
       </c>
       <c r="D65" t="s">
         <v>455</v>
@@ -36171,7 +36129,7 @@
       </c>
       <c r="C67" s="33" cm="1">
         <f t="array" ref="C67">INDEX(Data_EOLES!$J$1:$EK$191,MATCH(A67,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>21.749199999999998</v>
+        <v>24.940899999999999</v>
       </c>
       <c r="D67" t="s">
         <v>455</v>
@@ -36186,7 +36144,7 @@
       </c>
       <c r="C68" s="33" cm="1">
         <f t="array" ref="C68">INDEX(Data_EOLES!$J$1:$EK$191,MATCH(A68,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>2.1027999999999998</v>
+        <v>2.0373000000000001</v>
       </c>
       <c r="D68" t="s">
         <v>455</v>
@@ -36216,7 +36174,7 @@
       </c>
       <c r="C70" s="33" cm="1">
         <f t="array" ref="C70">INDEX(Data_EOLES!$J$1:$EK$191,MATCH(A70,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>18.366299999999999</v>
+        <v>18.846399999999999</v>
       </c>
       <c r="D70" t="s">
         <v>455</v>
@@ -36234,7 +36192,7 @@
       </c>
       <c r="C72" s="35">
         <f>SUM(C64:C68)+C70</f>
-        <v>46.296599999999998</v>
+        <v>49.764499999999998</v>
       </c>
       <c r="D72" s="36" t="s">
         <v>423</v>
@@ -36367,7 +36325,7 @@
       </c>
       <c r="B1" s="31">
         <f>INDEX(traitement_nW_EOLES!$C:$C,MATCH($A1,traitement_nW_EOLES!$A:$A,0))</f>
-        <v>519.77072999999996</v>
+        <v>504.1583700000001</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -36376,7 +36334,7 @@
       </c>
       <c r="B2" s="30">
         <f>INDEX(traitement_nW_EOLES!$C:$C,MATCH($A2,traitement_nW_EOLES!$A:$A,0))</f>
-        <v>0.61603241922966412</v>
+        <v>0.5254803927295767</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -36385,7 +36343,7 @@
       </c>
       <c r="B3" s="30">
         <f>INDEX(traitement_nW_EOLES!$C:$C,MATCH($A3,traitement_nW_EOLES!$A:$A,0))</f>
-        <v>0.95919465037848095</v>
+        <v>0.77349342641221619</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -36394,7 +36352,7 @@
       </c>
       <c r="B4" s="31">
         <f>INDEX(traitement_nW_EOLES!$C:$C,MATCH($A4,traitement_nW_EOLES!$A:$A,0))</f>
-        <v>142.65514000000002</v>
+        <v>127.44288</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -36403,7 +36361,7 @@
       </c>
       <c r="B5" s="30">
         <f>INDEX(traitement_nW_EOLES!$C:$C,MATCH($A5,traitement_nW_EOLES!$A:$A,0))</f>
-        <v>0.17327994647438125</v>
+        <v>0.12403560979228588</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -36412,7 +36370,7 @@
       </c>
       <c r="B6" s="31">
         <f>INDEX(traitement_nW_EOLES!$C:$C,MATCH($A6,traitement_nW_EOLES!$A:$A,0))</f>
-        <v>46.296599999999998</v>
+        <v>49.764499999999998</v>
       </c>
     </row>
   </sheetData>
@@ -36425,7 +36383,7 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.5546875" customWidth="1"/>
@@ -36447,7 +36405,7 @@
         <v>90</v>
       </c>
       <c r="B2">
-        <v>2050</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -36604,32 +36562,48 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>101</v>
-      </c>
-      <c r="B19" s="31" cm="1">
-        <f t="array" ref="B19">INDEX(Data_EOLES!$J$1:$EK$191,MATCH(A19,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>78.044830000000005</v>
-      </c>
-      <c r="C19" t="s">
-        <v>102</v>
+        <v>638</v>
+      </c>
+      <c r="B19">
+        <v>0.2</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>639</v>
       </c>
       <c r="B20">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>101</v>
+      </c>
+      <c r="B21" s="31" cm="1">
+        <f t="array" ref="B21">INDEX(Data_EOLES!$J$1:$EK$191,MATCH(A21,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
+        <v>12.85092</v>
+      </c>
+      <c r="C21" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>621</v>
       </c>
-      <c r="B21">
+      <c r="B23">
         <v>240</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C23" t="s">
         <v>102</v>
       </c>
     </row>
@@ -38024,7 +37998,7 @@
       </c>
       <c r="G30" s="28" cm="1">
         <f t="array" ref="G30">INDEX(Data_EOLES!$J$1:$EK$191,MATCH(G$1&amp;"_"&amp;$A30,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))</f>
-        <v>0.67191000000000001</v>
+        <v>0.67827000000000004</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
@@ -38033,7 +38007,7 @@
       </c>
       <c r="G31" s="28" cm="1">
         <f t="array" ref="G31">INDEX(Data_EOLES!$J$1:$EK$191,MATCH(G$1&amp;"_"&amp;$A31,Data_EOLES!$C:$C,0),MATCH(year_simulated,VALUE(Data_EOLES!$J$1:$EK$1),0))*G30</f>
-        <v>0.5565632103</v>
+        <v>0.56183138910000008</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
